--- a/docs/demo-import/题库导入_化学_演示.xlsx
+++ b/docs/demo-import/题库导入_化学_演示.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="题目检查" sheetId="1" r:id="Ra370904705484849"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="Ra92524343594468b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="题目检查" sheetId="1" r:id="Ra7f3b0020d124fab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R6d94caf68e424c46"/>
   </x:sheets>
 </x:workbook>
 </file>
